--- a/output/Gym_Butce_Takip.xlsx
+++ b/output/Gym_Butce_Takip.xlsx
@@ -702,7 +702,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev E · 17 Eylül 2026 · Tutarlar KDV hariç</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev F · 17 Eylül 2026 · Tutarlar KDV hariç</t>
         </is>
       </c>
     </row>
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="E15" s="8" t="n">
-        <v>514423</v>
+        <v>540728</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>866708</v>
+        <v>909501</v>
       </c>
       <c r="G15" s="9" t="n"/>
       <c r="H15" s="10" t="n">
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="E16" s="19" t="n">
-        <v>402580</v>
+        <v>412220</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>682600</v>
+        <v>698140</v>
       </c>
       <c r="G16" s="9" t="n"/>
       <c r="H16" s="20" t="n">
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="E17" s="8" t="n">
-        <v>542195</v>
+        <v>548666</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>845264</v>
+        <v>855764</v>
       </c>
       <c r="G17" s="9" t="n"/>
       <c r="H17" s="10" t="n">
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="E18" s="19" t="n">
-        <v>533159</v>
+        <v>539521</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>831176</v>
+        <v>841501</v>
       </c>
       <c r="G18" s="9" t="n"/>
       <c r="H18" s="20" t="n">
@@ -2154,7 +2154,7 @@
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>690566</v>
+        <v>725114</v>
       </c>
       <c r="D15" s="37" t="n"/>
       <c r="E15" s="37" t="n"/>
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="C16" s="39" t="n">
-        <v>542590</v>
+        <v>555180</v>
       </c>
       <c r="D16" s="37" t="n"/>
       <c r="E16" s="37" t="n"/>
@@ -2196,7 +2196,7 @@
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>693730</v>
+        <v>702215</v>
       </c>
       <c r="D17" s="37" t="n"/>
       <c r="E17" s="37" t="n"/>
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="C18" s="39" t="n">
-        <v>682168</v>
+        <v>690511</v>
       </c>
       <c r="D18" s="37" t="n"/>
       <c r="E18" s="37" t="n"/>

--- a/output/Gym_Butce_Takip.xlsx
+++ b/output/Gym_Butce_Takip.xlsx
@@ -702,7 +702,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev F · 17 Eylül 2026 · Tutarlar KDV hariç</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev G · 17 Eylül 2026 · Tutarlar KDV hariç</t>
         </is>
       </c>
     </row>

--- a/output/Gym_Butce_Takip.xlsx
+++ b/output/Gym_Butce_Takip.xlsx
@@ -702,7 +702,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev G · 17 Eylül 2026 · Tutarlar KDV hariç</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev H · 17 Eylül 2026 · Tutarlar KDV hariç</t>
         </is>
       </c>
     </row>

--- a/output/Gym_Butce_Takip.xlsx
+++ b/output/Gym_Butce_Takip.xlsx
@@ -792,10 +792,10 @@
         </is>
       </c>
       <c r="E5" s="8" t="n">
-        <v>155794</v>
+        <v>155584</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>247876</v>
+        <v>247578</v>
       </c>
       <c r="G5" s="9" t="n"/>
       <c r="H5" s="10" t="n">
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="E6" s="19" t="n">
-        <v>354543</v>
+        <v>347976</v>
       </c>
       <c r="F6" s="19" t="n">
-        <v>450588</v>
+        <v>442263</v>
       </c>
       <c r="G6" s="9" t="n"/>
       <c r="H6" s="20" t="n">
@@ -880,10 +880,10 @@
         </is>
       </c>
       <c r="E7" s="8" t="n">
-        <v>86050</v>
+        <v>85690</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>122188</v>
+        <v>121692</v>
       </c>
       <c r="G7" s="9" t="n"/>
       <c r="H7" s="10" t="n">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="E8" s="19" t="n">
-        <v>254653</v>
+        <v>260316</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>377585</v>
+        <v>386458</v>
       </c>
       <c r="G8" s="9" t="n"/>
       <c r="H8" s="20" t="n">
@@ -968,10 +968,10 @@
         </is>
       </c>
       <c r="E9" s="8" t="n">
-        <v>102629</v>
+        <v>99653</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>152964</v>
+        <v>148560</v>
       </c>
       <c r="G9" s="9" t="n"/>
       <c r="H9" s="10" t="n">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E10" s="19" t="n">
-        <v>309829</v>
+        <v>328251</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>466315</v>
+        <v>495718</v>
       </c>
       <c r="G10" s="9" t="n"/>
       <c r="H10" s="20" t="n">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="E15" s="8" t="n">
-        <v>540728</v>
+        <v>539693</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>909501</v>
+        <v>907712</v>
       </c>
       <c r="G15" s="9" t="n"/>
       <c r="H15" s="10" t="n">
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="E16" s="19" t="n">
-        <v>412220</v>
+        <v>412340</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>698140</v>
+        <v>698350</v>
       </c>
       <c r="G16" s="9" t="n"/>
       <c r="H16" s="20" t="n">
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="E17" s="8" t="n">
-        <v>548666</v>
+        <v>551015</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>855764</v>
+        <v>859935</v>
       </c>
       <c r="G17" s="9" t="n"/>
       <c r="H17" s="10" t="n">
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="E18" s="19" t="n">
-        <v>539521</v>
+        <v>541832</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>841501</v>
+        <v>845603</v>
       </c>
       <c r="G18" s="9" t="n"/>
       <c r="H18" s="20" t="n">
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="C5" s="36" t="n">
-        <v>201835</v>
+        <v>201581</v>
       </c>
       <c r="D5" s="37" t="n"/>
       <c r="E5" s="37" t="n"/>
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="C6" s="39" t="n">
-        <v>402566</v>
+        <v>395119</v>
       </c>
       <c r="D6" s="37" t="n"/>
       <c r="E6" s="37" t="n"/>
@@ -1986,7 +1986,7 @@
         </is>
       </c>
       <c r="C7" s="36" t="n">
-        <v>104119</v>
+        <v>103691</v>
       </c>
       <c r="D7" s="37" t="n"/>
       <c r="E7" s="37" t="n"/>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="C8" s="39" t="n">
-        <v>316119</v>
+        <v>323387</v>
       </c>
       <c r="D8" s="37" t="n"/>
       <c r="E8" s="37" t="n"/>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="C9" s="36" t="n">
-        <v>127797</v>
+        <v>124107</v>
       </c>
       <c r="D9" s="37" t="n"/>
       <c r="E9" s="37" t="n"/>
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="C10" s="39" t="n">
-        <v>388072</v>
+        <v>411984</v>
       </c>
       <c r="D10" s="37" t="n"/>
       <c r="E10" s="37" t="n"/>
@@ -2154,7 +2154,7 @@
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>725114</v>
+        <v>723702</v>
       </c>
       <c r="D15" s="37" t="n"/>
       <c r="E15" s="37" t="n"/>
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="C16" s="39" t="n">
-        <v>555180</v>
+        <v>555345</v>
       </c>
       <c r="D16" s="37" t="n"/>
       <c r="E16" s="37" t="n"/>
@@ -2196,7 +2196,7 @@
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>702215</v>
+        <v>705475</v>
       </c>
       <c r="D17" s="37" t="n"/>
       <c r="E17" s="37" t="n"/>
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="C18" s="39" t="n">
-        <v>690511</v>
+        <v>693717</v>
       </c>
       <c r="D18" s="37" t="n"/>
       <c r="E18" s="37" t="n"/>

--- a/output/Gym_Butce_Takip.xlsx
+++ b/output/Gym_Butce_Takip.xlsx
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="E15" s="8" t="n">
-        <v>539693</v>
+        <v>537495</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>907712</v>
+        <v>904040</v>
       </c>
       <c r="G15" s="9" t="n"/>
       <c r="H15" s="10" t="n">
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="E17" s="8" t="n">
-        <v>551015</v>
+        <v>550620</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>859935</v>
+        <v>859274</v>
       </c>
       <c r="G17" s="9" t="n"/>
       <c r="H17" s="10" t="n">
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="E18" s="19" t="n">
-        <v>541832</v>
+        <v>541443</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>845603</v>
+        <v>844953</v>
       </c>
       <c r="G18" s="9" t="n"/>
       <c r="H18" s="20" t="n">
@@ -2154,7 +2154,7 @@
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>723702</v>
+        <v>720768</v>
       </c>
       <c r="D15" s="37" t="n"/>
       <c r="E15" s="37" t="n"/>
@@ -2196,7 +2196,7 @@
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>705475</v>
+        <v>704947</v>
       </c>
       <c r="D17" s="37" t="n"/>
       <c r="E17" s="37" t="n"/>
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="C18" s="39" t="n">
-        <v>693717</v>
+        <v>693198</v>
       </c>
       <c r="D18" s="37" t="n"/>
       <c r="E18" s="37" t="n"/>
